--- a/internal_doc/05.测试设计/可靠性测试/基本操作故障测试设计.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/基本操作故障测试设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="120" windowWidth="12390" windowHeight="5670" activeTab="3"/>
+    <workbookView xWindow="6090" yWindow="120" windowWidth="12390" windowHeight="5670" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="普通表" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">普通表!$A$1:$G$414</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -157,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3071" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="309">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -914,10 +913,6 @@
     <t>w=2时两个备主机异常重启</t>
   </si>
   <si>
-    <t>连接的coord故障&gt;超时时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>连接的coord故障&lt;超时时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -968,52 +963,14 @@
     <t>数据节点故障</t>
   </si>
   <si>
-    <t>cata数据节点故障</t>
-  </si>
-  <si>
-    <t>数据节点故障&lt;超时时间</t>
-  </si>
-  <si>
-    <t>数据节点故障&gt;超时时间</t>
-  </si>
-  <si>
-    <t>数据节点发不出去</t>
-  </si>
-  <si>
-    <t>cata数据节点发不出去</t>
-  </si>
-  <si>
     <t>数据库节点故障</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cata数据节点发不出去</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cata故障在此处覆盖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord故障在此处覆盖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>组合异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多次kill-9kill-15</t>
-  </si>
-  <si>
-    <t>时间频繁跳变后，主节点主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>h3g3d1时连续杀同一个节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>虚存为8G</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1287,6 +1244,29 @@
   </si>
   <si>
     <t>时间提前，主节点进程正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据节点故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cata主节点发故障</t>
+  </si>
+  <si>
+    <t>连续杀同一个节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间延后，数据节点主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间提前，数据节点进程异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高并发为考虑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1593,7 +1573,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1647,12 +1627,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1662,12 +1642,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1676,21 +1656,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -2119,7 +2101,7 @@
       <c r="E3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="49" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="4"/>
@@ -2145,7 +2127,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="56"/>
       <c r="E5" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -2175,7 +2157,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="57"/>
       <c r="E7" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>24</v>
@@ -2221,7 +2203,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="56"/>
       <c r="E10" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -2249,7 +2231,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="57"/>
       <c r="E12" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -2317,7 +2299,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -2335,7 +2317,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="59"/>
       <c r="E17" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -2363,7 +2345,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>138</v>
@@ -2395,7 +2377,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -2469,7 +2451,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -2591,7 +2573,7 @@
       <c r="C34" s="4"/>
       <c r="D34" s="56"/>
       <c r="E34" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -2603,7 +2585,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="56"/>
       <c r="E35" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -2629,7 +2611,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="57"/>
       <c r="E37" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>24</v>
@@ -2705,7 +2687,7 @@
       <c r="C42" s="4"/>
       <c r="D42" s="56"/>
       <c r="E42" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -2717,7 +2699,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="56"/>
       <c r="E43" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -2729,7 +2711,7 @@
       <c r="C44" s="4"/>
       <c r="D44" s="56"/>
       <c r="E44" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -2741,7 +2723,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="57"/>
       <c r="E45" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
@@ -2793,7 +2775,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -2805,7 +2787,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -2831,7 +2813,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>24</v>
@@ -2847,7 +2829,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="58" t="s">
+      <c r="D52" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -2891,7 +2873,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="60"/>
       <c r="E55" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
@@ -2971,7 +2953,7 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -2983,7 +2965,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -3009,7 +2991,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>88</v>
@@ -3083,7 +3065,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -3095,7 +3077,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -3107,7 +3089,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -3119,7 +3101,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
@@ -3207,7 +3189,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="56"/>
       <c r="E77" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -3219,7 +3201,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="56"/>
       <c r="E78" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -3245,7 +3227,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="57"/>
       <c r="E80" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>24</v>
@@ -3311,7 +3293,7 @@
       <c r="C85" s="4"/>
       <c r="D85" s="56"/>
       <c r="E85" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
@@ -3325,7 +3307,7 @@
       <c r="C86" s="4"/>
       <c r="D86" s="56"/>
       <c r="E86" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -3349,7 +3331,7 @@
       <c r="C88" s="4"/>
       <c r="D88" s="57"/>
       <c r="E88" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -3395,7 +3377,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4" t="s">
@@ -3409,7 +3391,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -3435,7 +3417,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>24</v>
@@ -3449,7 +3431,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="58" t="s">
+      <c r="D95" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -3491,7 +3473,7 @@
       <c r="C98" s="4"/>
       <c r="D98" s="60"/>
       <c r="E98" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -3563,7 +3545,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -3575,7 +3557,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -3603,7 +3585,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>88</v>
@@ -3667,7 +3649,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -3679,7 +3661,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -3703,7 +3685,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -6897,7 +6879,7 @@
     </row>
     <row r="344" spans="1:9" s="9" customFormat="1">
       <c r="A344" s="8"/>
-      <c r="B344" s="61" t="s">
+      <c r="B344" s="58" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -7871,7 +7853,7 @@
       <c r="C414" s="4"/>
       <c r="D414" s="4"/>
       <c r="E414" s="6" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F414" s="4"/>
       <c r="G414" s="4"/>
@@ -7880,6 +7862,35 @@
   </sheetData>
   <autoFilter ref="A1:G414"/>
   <mergeCells count="40">
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="D119:D121"/>
+    <mergeCell ref="D30:D37"/>
+    <mergeCell ref="D38:D45"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D73:D80"/>
+    <mergeCell ref="D81:D88"/>
+    <mergeCell ref="D95:D98"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="D179:D181"/>
+    <mergeCell ref="D197:D203"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="D400:D401"/>
+    <mergeCell ref="B344:B350"/>
+    <mergeCell ref="D352:D355"/>
+    <mergeCell ref="D356:D359"/>
+    <mergeCell ref="D363:D365"/>
+    <mergeCell ref="D375:D377"/>
+    <mergeCell ref="D378:D380"/>
+    <mergeCell ref="D383:D384"/>
+    <mergeCell ref="D392:D394"/>
+    <mergeCell ref="D395:D397"/>
     <mergeCell ref="D324:D328"/>
     <mergeCell ref="D209:D213"/>
     <mergeCell ref="D191:D196"/>
@@ -7891,35 +7902,6 @@
     <mergeCell ref="D285:D289"/>
     <mergeCell ref="D305:D311"/>
     <mergeCell ref="D312:D318"/>
-    <mergeCell ref="D400:D401"/>
-    <mergeCell ref="B344:B350"/>
-    <mergeCell ref="D352:D355"/>
-    <mergeCell ref="D356:D359"/>
-    <mergeCell ref="D363:D365"/>
-    <mergeCell ref="D375:D377"/>
-    <mergeCell ref="D378:D380"/>
-    <mergeCell ref="D383:D384"/>
-    <mergeCell ref="D392:D394"/>
-    <mergeCell ref="D395:D397"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D176:D178"/>
-    <mergeCell ref="D179:D181"/>
-    <mergeCell ref="D197:D203"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D116:D118"/>
-    <mergeCell ref="D119:D121"/>
-    <mergeCell ref="D30:D37"/>
-    <mergeCell ref="D38:D45"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="D73:D80"/>
-    <mergeCell ref="D81:D88"/>
-    <mergeCell ref="D95:D98"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8020,7 +8002,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="56"/>
       <c r="E5" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -8046,7 +8028,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="57"/>
       <c r="E7" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>24</v>
@@ -8085,7 +8067,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="56"/>
       <c r="E10" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -8109,7 +8091,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="57"/>
       <c r="E12" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -8167,7 +8149,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -8182,7 +8164,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="59"/>
       <c r="E17" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -8208,7 +8190,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>138</v>
@@ -8234,7 +8216,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -8299,7 +8281,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -8407,7 +8389,7 @@
       <c r="C34" s="4"/>
       <c r="D34" s="56"/>
       <c r="E34" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -8418,7 +8400,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="56"/>
       <c r="E35" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -8442,7 +8424,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="57"/>
       <c r="E37" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>24</v>
@@ -8505,7 +8487,7 @@
       <c r="C42" s="4"/>
       <c r="D42" s="56"/>
       <c r="E42" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -8516,7 +8498,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="56"/>
       <c r="E43" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -8527,7 +8509,7 @@
       <c r="C44" s="4"/>
       <c r="D44" s="56"/>
       <c r="E44" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -8538,7 +8520,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="57"/>
       <c r="E45" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
@@ -8583,7 +8565,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -8594,7 +8576,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -8618,7 +8600,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>24</v>
@@ -8633,7 +8615,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="58" t="s">
+      <c r="D52" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -8670,7 +8652,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="60"/>
       <c r="E55" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
@@ -8737,7 +8719,7 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -8748,7 +8730,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -8772,7 +8754,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>88</v>
@@ -8833,7 +8815,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -8844,7 +8826,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -8855,7 +8837,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -8866,7 +8848,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
@@ -8948,7 +8930,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="56"/>
       <c r="E77" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -8959,7 +8941,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="56"/>
       <c r="E78" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -8983,7 +8965,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="57"/>
       <c r="E80" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>24</v>
@@ -9044,7 +9026,7 @@
       <c r="C85" s="4"/>
       <c r="D85" s="56"/>
       <c r="E85" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
@@ -9057,7 +9039,7 @@
       <c r="C86" s="4"/>
       <c r="D86" s="56"/>
       <c r="E86" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -9079,7 +9061,7 @@
       <c r="C88" s="4"/>
       <c r="D88" s="57"/>
       <c r="E88" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -9122,7 +9104,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4" t="s">
@@ -9135,7 +9117,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -9159,7 +9141,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>24</v>
@@ -9172,7 +9154,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="58" t="s">
+      <c r="D95" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -9211,7 +9193,7 @@
       <c r="C98" s="4"/>
       <c r="D98" s="60"/>
       <c r="E98" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -9278,7 +9260,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -9289,7 +9271,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -9315,7 +9297,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>88</v>
@@ -9374,7 +9356,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -9385,7 +9367,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -9407,7 +9389,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -12363,7 +12345,7 @@
     </row>
     <row r="344" spans="1:7" s="9" customFormat="1">
       <c r="A344" s="8"/>
-      <c r="B344" s="61" t="s">
+      <c r="B344" s="58" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -13278,6 +13260,37 @@
     <row r="426" ht="13.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="D285:D289"/>
+    <mergeCell ref="D305:D311"/>
+    <mergeCell ref="D312:D318"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="B344:B350"/>
+    <mergeCell ref="D119:D121"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D73:D80"/>
+    <mergeCell ref="D81:D88"/>
+    <mergeCell ref="D95:D98"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D30:D37"/>
+    <mergeCell ref="D38:D45"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="D179:D181"/>
+    <mergeCell ref="D191:D196"/>
+    <mergeCell ref="D197:D203"/>
+    <mergeCell ref="D209:D213"/>
+    <mergeCell ref="D227:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="D266:D272"/>
+    <mergeCell ref="D273:D279"/>
     <mergeCell ref="D383:D384"/>
     <mergeCell ref="D392:D394"/>
     <mergeCell ref="D395:D397"/>
@@ -13287,37 +13300,6 @@
     <mergeCell ref="D363:D365"/>
     <mergeCell ref="D375:D377"/>
     <mergeCell ref="D378:D380"/>
-    <mergeCell ref="D227:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D246:D250"/>
-    <mergeCell ref="D266:D272"/>
-    <mergeCell ref="D273:D279"/>
-    <mergeCell ref="D176:D178"/>
-    <mergeCell ref="D179:D181"/>
-    <mergeCell ref="D191:D196"/>
-    <mergeCell ref="D197:D203"/>
-    <mergeCell ref="D209:D213"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D30:D37"/>
-    <mergeCell ref="D38:D45"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="D73:D80"/>
-    <mergeCell ref="D81:D88"/>
-    <mergeCell ref="D95:D98"/>
-    <mergeCell ref="D116:D118"/>
-    <mergeCell ref="D119:D121"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="D285:D289"/>
-    <mergeCell ref="D305:D311"/>
-    <mergeCell ref="D312:D318"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="B344:B350"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13423,7 +13405,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="56"/>
       <c r="E5" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -13449,7 +13431,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="57"/>
       <c r="E7" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>24</v>
@@ -13488,7 +13470,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="56"/>
       <c r="E10" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -13512,7 +13494,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="57"/>
       <c r="E12" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -13570,7 +13552,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -13585,7 +13567,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="59"/>
       <c r="E17" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -13611,7 +13593,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>138</v>
@@ -13637,7 +13619,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -13702,7 +13684,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -13810,7 +13792,7 @@
       <c r="C34" s="4"/>
       <c r="D34" s="56"/>
       <c r="E34" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -13821,7 +13803,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="56"/>
       <c r="E35" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -13845,7 +13827,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="57"/>
       <c r="E37" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>24</v>
@@ -13908,7 +13890,7 @@
       <c r="C42" s="4"/>
       <c r="D42" s="56"/>
       <c r="E42" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -13919,7 +13901,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="56"/>
       <c r="E43" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -13930,7 +13912,7 @@
       <c r="C44" s="4"/>
       <c r="D44" s="56"/>
       <c r="E44" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -13941,7 +13923,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="57"/>
       <c r="E45" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4" t="s">
@@ -13986,7 +13968,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -13997,7 +13979,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -14021,7 +14003,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>24</v>
@@ -14036,7 +14018,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="58" t="s">
+      <c r="D52" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -14073,7 +14055,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="60"/>
       <c r="E55" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4" t="s">
@@ -14140,7 +14122,7 @@
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -14151,7 +14133,7 @@
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -14175,7 +14157,7 @@
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>88</v>
@@ -14236,7 +14218,7 @@
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
@@ -14247,7 +14229,7 @@
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
@@ -14258,7 +14240,7 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -14269,7 +14251,7 @@
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
@@ -14351,7 +14333,7 @@
       <c r="C77" s="4"/>
       <c r="D77" s="56"/>
       <c r="E77" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
@@ -14362,7 +14344,7 @@
       <c r="C78" s="4"/>
       <c r="D78" s="56"/>
       <c r="E78" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -14386,7 +14368,7 @@
       <c r="C80" s="4"/>
       <c r="D80" s="57"/>
       <c r="E80" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>24</v>
@@ -14447,7 +14429,7 @@
       <c r="C85" s="4"/>
       <c r="D85" s="56"/>
       <c r="E85" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
@@ -14460,7 +14442,7 @@
       <c r="C86" s="4"/>
       <c r="D86" s="56"/>
       <c r="E86" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
@@ -14482,7 +14464,7 @@
       <c r="C88" s="4"/>
       <c r="D88" s="57"/>
       <c r="E88" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -14525,7 +14507,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4" t="s">
@@ -14538,7 +14520,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -14562,7 +14544,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>24</v>
@@ -14575,7 +14557,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="58" t="s">
+      <c r="D95" s="61" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -14614,7 +14596,7 @@
       <c r="C98" s="4"/>
       <c r="D98" s="60"/>
       <c r="E98" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -14681,7 +14663,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
@@ -14692,7 +14674,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
@@ -14718,7 +14700,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>88</v>
@@ -14777,7 +14759,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -14788,7 +14770,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4"/>
@@ -14810,7 +14792,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -17766,7 +17748,7 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="8"/>
-      <c r="B344" s="61" t="s">
+      <c r="B344" s="58" t="s">
         <v>106</v>
       </c>
       <c r="C344" s="8"/>
@@ -18678,21 +18660,16 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D378:D380"/>
-    <mergeCell ref="D383:D384"/>
-    <mergeCell ref="D392:D394"/>
-    <mergeCell ref="D395:D397"/>
-    <mergeCell ref="D400:D401"/>
-    <mergeCell ref="D273:D279"/>
-    <mergeCell ref="D285:D289"/>
-    <mergeCell ref="D305:D311"/>
-    <mergeCell ref="D312:D318"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="D191:D196"/>
-    <mergeCell ref="D197:D203"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="B344:B350"/>
+    <mergeCell ref="D352:D355"/>
+    <mergeCell ref="D356:D359"/>
+    <mergeCell ref="D363:D365"/>
+    <mergeCell ref="D375:D377"/>
+    <mergeCell ref="D209:D213"/>
+    <mergeCell ref="D227:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="D266:D272"/>
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="D8:D12"/>
     <mergeCell ref="D16:D18"/>
@@ -18708,16 +18685,21 @@
     <mergeCell ref="D119:D121"/>
     <mergeCell ref="D131:D133"/>
     <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D209:D213"/>
-    <mergeCell ref="D227:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D246:D250"/>
-    <mergeCell ref="D266:D272"/>
-    <mergeCell ref="B344:B350"/>
-    <mergeCell ref="D352:D355"/>
-    <mergeCell ref="D356:D359"/>
-    <mergeCell ref="D363:D365"/>
-    <mergeCell ref="D375:D377"/>
+    <mergeCell ref="D191:D196"/>
+    <mergeCell ref="D197:D203"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D273:D279"/>
+    <mergeCell ref="D285:D289"/>
+    <mergeCell ref="D305:D311"/>
+    <mergeCell ref="D312:D318"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="D378:D380"/>
+    <mergeCell ref="D383:D384"/>
+    <mergeCell ref="D392:D394"/>
+    <mergeCell ref="D395:D397"/>
+    <mergeCell ref="D400:D401"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18759,117 +18741,117 @@
         <v>185</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F2" s="28" t="s">
         <v>199</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="31" customFormat="1">
       <c r="A3" s="32"/>
       <c r="B3" s="33" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="32"/>
       <c r="G3" s="34" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H3" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="31" customFormat="1">
       <c r="A4" s="32"/>
       <c r="B4" s="33" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="32"/>
       <c r="G4" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="31" customFormat="1">
       <c r="A5" s="35"/>
       <c r="B5" s="43" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F5" s="35"/>
       <c r="G5" s="37" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="31" customFormat="1">
       <c r="A6" s="32"/>
       <c r="B6" s="38" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="31" customFormat="1">
@@ -18877,167 +18859,167 @@
         <v>27</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="31" customFormat="1">
       <c r="A8" s="32"/>
       <c r="B8" s="33" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F8" s="33"/>
       <c r="G8" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H8" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="31" customFormat="1">
       <c r="A9" s="32"/>
       <c r="B9" s="33" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="33"/>
       <c r="G9" s="34" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="31" customFormat="1">
       <c r="A10" s="32"/>
       <c r="B10" s="33" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="33"/>
       <c r="G10" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="31" customFormat="1">
       <c r="A11" s="32"/>
       <c r="B11" s="33" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="33"/>
       <c r="G11" s="34" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="31" customFormat="1">
       <c r="A12" s="32"/>
       <c r="B12" s="33" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="33"/>
       <c r="G12" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="31" customFormat="1">
       <c r="A13" s="35"/>
       <c r="B13" s="36" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F13" s="36"/>
       <c r="G13" s="37" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="31" customFormat="1">
       <c r="A14" s="32"/>
       <c r="B14" s="38" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="31" customFormat="1">
@@ -19045,147 +19027,147 @@
         <v>127</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F15" s="29" t="s">
         <v>200</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="31" customFormat="1">
       <c r="A16" s="32"/>
       <c r="B16" s="33" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="F16" s="33"/>
       <c r="G16" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="31" customFormat="1">
       <c r="A17" s="32"/>
       <c r="B17" s="33" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="33"/>
       <c r="G17" s="34" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="31" customFormat="1">
       <c r="A18" s="32"/>
       <c r="B18" s="33" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="33"/>
       <c r="G18" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="31" customFormat="1">
       <c r="A19" s="32"/>
       <c r="B19" s="33" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="33"/>
       <c r="G19" s="34" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="31" customFormat="1">
       <c r="A20" s="32"/>
       <c r="B20" s="33" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="33"/>
       <c r="G20" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="31" customFormat="1">
       <c r="A21" s="32"/>
       <c r="B21" s="38" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="F21" s="33"/>
       <c r="G21" s="37" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="31" customFormat="1">
       <c r="A22" s="35"/>
       <c r="B22" s="36" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="F22" s="36"/>
       <c r="G22" s="37" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="31" customFormat="1">
@@ -19206,10 +19188,10 @@
       </c>
       <c r="F23" s="29"/>
       <c r="G23" s="30" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="31" customFormat="1">
@@ -19226,10 +19208,10 @@
       <c r="E24" s="34"/>
       <c r="F24" s="33"/>
       <c r="G24" s="34" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="31" customFormat="1">
@@ -19249,7 +19231,7 @@
       <c r="F25" s="33"/>
       <c r="G25" s="34"/>
       <c r="I25" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="31" customFormat="1">
@@ -19268,10 +19250,10 @@
       </c>
       <c r="F26" s="36"/>
       <c r="G26" s="37" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I26" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -19279,55 +19261,55 @@
         <v>186</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="F27" s="53"/>
+        <v>255</v>
+      </c>
+      <c r="F27" s="50"/>
       <c r="G27" s="25" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I27" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="E28" s="17"/>
       <c r="F28" s="16"/>
       <c r="G28" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I28" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="18"/>
       <c r="B29" s="26" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C29" s="44" t="s">
         <v>156</v>
@@ -19336,15 +19318,15 @@
         <v>156</v>
       </c>
       <c r="E29" s="27"/>
-      <c r="F29" s="54"/>
+      <c r="F29" s="51"/>
       <c r="G29" s="27" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I29" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -19352,65 +19334,65 @@
         <v>187</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F30" s="24" t="s">
         <v>200</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="15"/>
       <c r="B31" s="16" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="16"/>
       <c r="G31" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="18"/>
       <c r="B32" s="26" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E32" s="27"/>
-      <c r="F32" s="54"/>
+      <c r="F32" s="51"/>
       <c r="G32" s="27" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -19418,40 +19400,40 @@
         <v>188</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F33" s="24" t="s">
         <v>200</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H33" s="22"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="15"/>
       <c r="B34" s="16" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="16"/>
       <c r="G34" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -19466,9 +19448,9 @@
         <v>157</v>
       </c>
       <c r="E35" s="27"/>
-      <c r="F35" s="54"/>
+      <c r="F35" s="51"/>
       <c r="G35" s="27" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -19476,65 +19458,65 @@
         <v>189</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="F36" s="24" t="s">
         <v>200</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H36" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="16"/>
       <c r="G37" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H37" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="18"/>
       <c r="B38" s="44" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C38" s="44" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="E38" s="27"/>
-      <c r="F38" s="54"/>
+      <c r="F38" s="51"/>
       <c r="G38" s="27" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H38" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -19542,45 +19524,45 @@
         <v>190</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="F39" s="24" t="s">
         <v>200</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H39" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="15"/>
       <c r="B40" s="16" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="16"/>
       <c r="G40" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H40" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -19595,12 +19577,12 @@
         <v>161</v>
       </c>
       <c r="E41" s="27"/>
-      <c r="F41" s="54"/>
+      <c r="F41" s="51"/>
       <c r="G41" s="27" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H41" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="31" customFormat="1">
@@ -19608,101 +19590,101 @@
         <v>191</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="F42" s="29" t="s">
         <v>199</v>
       </c>
       <c r="G42" s="30" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I42" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="31" customFormat="1">
       <c r="A43" s="32"/>
       <c r="B43" s="33" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="E43" s="34"/>
       <c r="F43" s="33"/>
       <c r="G43" s="34" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I43" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="31" customFormat="1">
       <c r="A44" s="32"/>
       <c r="B44" s="33" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="F44" s="33"/>
       <c r="G44" s="34" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="31" customFormat="1">
       <c r="A45" s="35"/>
       <c r="B45" s="36" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D45" s="36" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="F45" s="36"/>
       <c r="G45" s="37" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I45" s="31" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -19710,149 +19692,149 @@
         <v>44</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="F46" s="24" t="s">
         <v>201</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I46" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="15"/>
       <c r="B47" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E47" s="17"/>
       <c r="F47" s="16"/>
       <c r="G47" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="I47" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="15"/>
       <c r="B48" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="16"/>
       <c r="G48" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I48" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="15"/>
       <c r="B49" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="F49" s="16"/>
       <c r="G49" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="I49" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="15"/>
       <c r="B50" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F50" s="16"/>
       <c r="G50" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I50" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="15"/>
       <c r="B51" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C51" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D51" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E51" s="42" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="F51" s="16"/>
       <c r="G51" s="23"/>
       <c r="I51" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="54" customFormat="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="51" customFormat="1">
       <c r="B52" s="26" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C52" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E52" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="I52" s="54" t="s">
-        <v>306</v>
+        <v>289</v>
+      </c>
+      <c r="I52" s="51" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -19860,151 +19842,151 @@
         <v>193</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="15"/>
       <c r="B54" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E54" s="17"/>
       <c r="F54" s="16"/>
       <c r="G54" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="15"/>
       <c r="B55" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="E55" s="17"/>
       <c r="F55" s="16"/>
       <c r="G55" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="15"/>
       <c r="B56" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="F56" s="16"/>
       <c r="G56" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="15"/>
       <c r="B57" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F57" s="16"/>
       <c r="G57" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="15"/>
       <c r="B58" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C58" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D58" s="41" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="E58" s="42" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="F58" s="16"/>
       <c r="G58" s="23"/>
       <c r="H58" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="18"/>
       <c r="B59" s="41" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C59" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="F59" s="54"/>
+        <v>280</v>
+      </c>
+      <c r="F59" s="51"/>
       <c r="G59" s="26" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -20012,151 +19994,151 @@
         <v>194</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="F60" s="24" t="s">
         <v>200</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="15"/>
       <c r="B61" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E61" s="17"/>
       <c r="F61" s="16"/>
       <c r="G61" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="15"/>
       <c r="B62" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="E62" s="17"/>
       <c r="F62" s="16"/>
       <c r="G62" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="15"/>
       <c r="B63" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="F63" s="16"/>
       <c r="G63" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="15"/>
       <c r="B64" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F64" s="16"/>
       <c r="G64" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="15"/>
       <c r="B65" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C65" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D65" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E65" s="42" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="F65" s="16"/>
       <c r="G65" s="23"/>
       <c r="H65" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="18"/>
       <c r="B66" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D66" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E66" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="F66" s="54"/>
+        <v>280</v>
+      </c>
+      <c r="F66" s="51"/>
       <c r="G66" s="26" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -20164,109 +20146,109 @@
         <v>195</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C67" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D67" s="24" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="F67" s="24" t="s">
         <v>200</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="15"/>
       <c r="B68" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E68" s="17"/>
       <c r="F68" s="16"/>
       <c r="G68" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="15"/>
       <c r="B69" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="E69" s="17"/>
       <c r="F69" s="16"/>
       <c r="G69" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="15"/>
       <c r="B70" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="F70" s="16"/>
       <c r="G70" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="15"/>
       <c r="B71" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D71" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F71" s="16"/>
       <c r="G71" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -20275,10 +20257,10 @@
         <v>48</v>
       </c>
       <c r="C72" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D72" s="41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E72" s="22" t="s">
         <v>48</v>
@@ -20286,29 +20268,29 @@
       <c r="F72" s="16"/>
       <c r="G72" s="23"/>
       <c r="H72" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="18"/>
       <c r="B73" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C73" s="44" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E73" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="F73" s="54"/>
+        <v>280</v>
+      </c>
+      <c r="F73" s="51"/>
       <c r="G73" s="23" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -20325,7 +20307,7 @@
     <row r="75" spans="1:8">
       <c r="A75" s="15"/>
       <c r="B75" s="62" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C75" s="62"/>
       <c r="D75" s="62"/>
@@ -20334,7 +20316,7 @@
     <row r="76" spans="1:8">
       <c r="A76" s="15"/>
       <c r="B76" s="62" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="C76" s="62"/>
       <c r="D76" s="62"/>
@@ -20343,7 +20325,7 @@
     <row r="77" spans="1:8">
       <c r="A77" s="15"/>
       <c r="B77" s="62" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C77" s="62"/>
       <c r="D77" s="62"/>
@@ -20352,7 +20334,7 @@
     <row r="78" spans="1:8">
       <c r="A78" s="15"/>
       <c r="B78" s="62" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="C78" s="62"/>
       <c r="D78" s="62"/>
@@ -20361,7 +20343,7 @@
     <row r="79" spans="1:8">
       <c r="A79" s="15"/>
       <c r="B79" s="62" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C79" s="62"/>
       <c r="D79" s="62"/>
@@ -20370,7 +20352,7 @@
     <row r="80" spans="1:8">
       <c r="A80" s="18"/>
       <c r="B80" s="62" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="C80" s="62"/>
       <c r="D80" s="62"/>
@@ -20378,111 +20360,111 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="B81" s="70" t="s">
-        <v>313</v>
-      </c>
-      <c r="C81" s="70" t="s">
-        <v>313</v>
-      </c>
-      <c r="D81" s="70" t="s">
-        <v>313</v>
+        <v>219</v>
+      </c>
+      <c r="B81" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="C81" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="D81" s="54" t="s">
+        <v>301</v>
       </c>
       <c r="E81" s="70" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="G81" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="15"/>
-      <c r="B82" s="68" t="s">
-        <v>312</v>
-      </c>
-      <c r="C82" s="68" t="s">
-        <v>312</v>
-      </c>
-      <c r="D82" s="68" t="s">
-        <v>312</v>
-      </c>
-      <c r="E82" s="68" t="s">
-        <v>312</v>
+      <c r="B82" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="C82" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="D82" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="E82" s="53" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="15"/>
-      <c r="B83" s="68" t="s">
-        <v>311</v>
-      </c>
-      <c r="C83" s="68"/>
-      <c r="D83" s="68"/>
-      <c r="E83" s="69"/>
+      <c r="B83" s="52" t="s">
+        <v>299</v>
+      </c>
+      <c r="C83" s="52"/>
+      <c r="D83" s="52"/>
+      <c r="E83" s="53"/>
       <c r="G83" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="15"/>
-      <c r="B84" s="68" t="s">
-        <v>310</v>
-      </c>
-      <c r="C84" s="68"/>
-      <c r="D84" s="68"/>
-      <c r="E84" s="69"/>
+      <c r="B84" s="52" t="s">
+        <v>298</v>
+      </c>
+      <c r="C84" s="52"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="53"/>
       <c r="G84" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="15"/>
-      <c r="B85" s="68"/>
-      <c r="C85" s="68"/>
-      <c r="E85" s="69" t="s">
-        <v>314</v>
+      <c r="B85" s="52"/>
+      <c r="C85" s="52"/>
+      <c r="E85" s="53" t="s">
+        <v>302</v>
       </c>
       <c r="G85" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="15"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68"/>
-      <c r="D86" s="68"/>
-      <c r="E86" s="69" t="s">
-        <v>299</v>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="53" t="s">
+        <v>287</v>
       </c>
       <c r="G86" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="18"/>
-      <c r="B87" s="66" t="s">
-        <v>239</v>
-      </c>
-      <c r="C87" s="66"/>
-      <c r="D87" s="66"/>
-      <c r="E87" s="67"/>
+      <c r="B87" s="64" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" s="64"/>
+      <c r="D87" s="64"/>
+      <c r="E87" s="65"/>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G88"/>
   <mergeCells count="8">
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B87:E87"/>
     <mergeCell ref="B79:E79"/>
     <mergeCell ref="B74:E74"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B87:E87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20492,7 +20474,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -20500,7 +20482,7 @@
     <col min="3" max="3" width="26.875" customWidth="1"/>
     <col min="4" max="4" width="26.25" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="25.25" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -20523,735 +20505,670 @@
         <v>185</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="31" customFormat="1">
       <c r="A3" s="32"/>
       <c r="B3" s="38" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="31" customFormat="1">
       <c r="A4" s="35"/>
-      <c r="B4" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>197</v>
+      <c r="B4" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="31" customFormat="1">
       <c r="A5" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>220</v>
+      <c r="B5" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="E5" s="69" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="31" customFormat="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="31" customFormat="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>205</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>227</v>
+      <c r="A6" s="35"/>
+      <c r="B6" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="29" customFormat="1">
+      <c r="A7" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="31" customFormat="1">
       <c r="A8" s="35"/>
       <c r="B8" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="31" customFormat="1">
+      <c r="A9" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C9" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D9" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E9" s="69" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="31" customFormat="1">
-      <c r="A9" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="31" customFormat="1">
       <c r="A10" s="32"/>
-      <c r="B10" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="31" customFormat="1">
-      <c r="A11" s="32"/>
-      <c r="B11" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="31" customFormat="1">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="31" customFormat="1">
-      <c r="A13" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="31" customFormat="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="31" customFormat="1">
-      <c r="A15" s="32"/>
-      <c r="B15" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="C15" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="E15" s="51" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="14" t="s">
+      <c r="B10" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="14" t="s">
+      <c r="B11" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F17" s="22"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="14" t="s">
+      <c r="B12" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F12" s="22"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B18" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F18" s="22"/>
+      <c r="B13" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" s="22"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" s="22"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F15" s="22"/>
+    </row>
+    <row r="16" spans="1:6" s="31" customFormat="1">
+      <c r="A16" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="31" customFormat="1">
+      <c r="A17" s="32"/>
+      <c r="B17" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="31" customFormat="1">
+      <c r="A18" s="35"/>
+      <c r="B18" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="14" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>218</v>
+        <v>303</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F19" s="22"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F20" s="22"/>
-    </row>
-    <row r="21" spans="1:6" s="31" customFormat="1">
-      <c r="A21" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="31" customFormat="1">
-      <c r="A22" s="32"/>
-      <c r="B22" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" s="31" customFormat="1">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>184</v>
-      </c>
+      <c r="A20" s="15"/>
+      <c r="B20" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>304</v>
+      </c>
+      <c r="F20" s="47"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="15"/>
+      <c r="B21" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="18"/>
+      <c r="B22" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F24" s="22"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="15"/>
-      <c r="B25" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>219</v>
-      </c>
-      <c r="F25" s="47" t="s">
-        <v>226</v>
-      </c>
+      <c r="B25" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F25" s="47"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="15"/>
-      <c r="B26" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>197</v>
+      <c r="A26" s="18"/>
+      <c r="B26" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="18"/>
-      <c r="B27" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>192</v>
-      </c>
+      <c r="A27" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F28" s="22"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="15"/>
       <c r="B29" s="41" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="15"/>
-      <c r="B30" s="22" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="15"/>
+      <c r="B32" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="15"/>
+      <c r="B33" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="D33" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="E33" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="F30" s="47" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="18"/>
-      <c r="B31" s="26" t="s">
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="18"/>
+      <c r="B34" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C34" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="67"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="15"/>
+      <c r="B36" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" s="62"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="63"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="15"/>
+      <c r="B37" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="62"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="63"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="15"/>
+      <c r="B38" s="62" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="63"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="15"/>
+      <c r="B39" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="63"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="15"/>
+      <c r="B40" s="62" t="s">
         <v>224</v>
       </c>
-      <c r="D31" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F32" s="22"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="15"/>
-      <c r="B33" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="E33" s="42" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="15"/>
-      <c r="B34" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="18"/>
-      <c r="B35" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F36" s="22"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="15"/>
-      <c r="B37" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="15"/>
-      <c r="B38" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="18"/>
-      <c r="B39" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C39" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B40" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="65"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="15"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="63"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="18"/>
       <c r="B41" s="62" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C41" s="62"/>
       <c r="D41" s="62"/>
       <c r="E41" s="63"/>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="15"/>
-      <c r="B42" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="63"/>
-    </row>
-    <row r="43" spans="1:6">
+    <row r="42" spans="1:7">
+      <c r="A42" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="D42" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="E42" s="70" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" s="15"/>
-      <c r="B43" s="62" t="s">
-        <v>234</v>
-      </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="62"/>
-      <c r="E43" s="63"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="B43" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="C43" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="E43" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="G43" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" s="15"/>
-      <c r="B44" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="63"/>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="B44" s="52" t="s">
+        <v>306</v>
+      </c>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="53"/>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="15"/>
-      <c r="B45" s="62" t="s">
-        <v>236</v>
-      </c>
-      <c r="C45" s="62"/>
-      <c r="D45" s="62"/>
-      <c r="E45" s="63"/>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="53" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="18"/>
-      <c r="B46" s="62" t="s">
-        <v>237</v>
-      </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="63"/>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="B47" s="64" t="s">
-        <v>229</v>
-      </c>
-      <c r="C47" s="64"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65"/>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="15"/>
-      <c r="B48" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="62"/>
-      <c r="E48" s="63"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="15"/>
-      <c r="B49" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="C49" s="62"/>
-      <c r="D49" s="62"/>
-      <c r="E49" s="63"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="18"/>
-      <c r="B50" s="66" t="s">
-        <v>231</v>
-      </c>
-      <c r="C50" s="66"/>
-      <c r="D50" s="66"/>
-      <c r="E50" s="67"/>
+      <c r="B46" s="71" t="s">
+        <v>305</v>
+      </c>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B45:E45"/>
+  <mergeCells count="7">
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
